--- a/Yield/RES_field_datasheet_jdx.xlsx
+++ b/Yield/RES_field_datasheet_jdx.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhangdakui/Documents/GitHub/ERW/Yield/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhang\Documents\GitHub\ERW\Yield\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB96D3AC-257A-984E-B1A4-C4B4775137FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{7065DB47-097C-C04F-ADEF-4C289C6D55B0}"/>
+    <workbookView xWindow="0" yWindow="765" windowWidth="30240" windowHeight="18885"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Plot</t>
   </si>
@@ -102,13 +101,37 @@
   </si>
   <si>
     <t>OD_Straw_g</t>
+  </si>
+  <si>
+    <t>Paper+Grains+Rubber_Band</t>
+  </si>
+  <si>
+    <t>(5xpaperbag+5Rubberband)/5</t>
+  </si>
+  <si>
+    <t>D=B-C</t>
+  </si>
+  <si>
+    <t>F=D-E</t>
+  </si>
+  <si>
+    <t>E=</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>HI=E/D</t>
+  </si>
+  <si>
+    <t>Usually around 0.51</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -472,17 +495,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF552B86-4BA9-0C49-BA29-956140839636}">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="26.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
     <col min="4" max="4" width="18.6640625" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -505,7 +528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -516,7 +539,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -527,7 +550,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -538,7 +561,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -549,7 +572,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -560,7 +583,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -571,7 +594,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -582,7 +605,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -593,7 +616,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -604,7 +627,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -615,7 +638,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -626,7 +649,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -637,7 +660,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -648,7 +671,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -659,7 +682,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -668,6 +691,38 @@
       </c>
       <c r="C16">
         <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="4:8">
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="4:8">
+      <c r="D19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="4:8">
+      <c r="D20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="4:8">
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Yield/RES_field_datasheet_jdx.xlsx
+++ b/Yield/RES_field_datasheet_jdx.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhang\Documents\GitHub\ERW\Yield\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhangdakui/Documents/GitHub/ERW/Yield/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B51E251-522D-E044-A9F1-CF4D4680251C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="765" windowWidth="30240" windowHeight="18885"/>
+    <workbookView xWindow="2820" yWindow="4340" windowWidth="27420" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Plot</t>
   </si>
@@ -103,35 +105,26 @@
     <t>OD_Straw_g</t>
   </si>
   <si>
-    <t>Paper+Grains+Rubber_Band</t>
-  </si>
-  <si>
     <t>(5xpaperbag+5Rubberband)/5</t>
   </si>
   <si>
-    <t>D=B-C</t>
-  </si>
-  <si>
-    <t>F=D-E</t>
-  </si>
-  <si>
-    <t>E=</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>HI=E/D</t>
-  </si>
-  <si>
-    <t>Usually around 0.51</t>
+    <t>Odgrain+paperbag+rubber</t>
+  </si>
+  <si>
+    <t>paperbag+rubber</t>
+  </si>
+  <si>
+    <t>OD grain</t>
+  </si>
+  <si>
+    <t>check</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -495,17 +488,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="26.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" customWidth="1"/>
     <col min="4" max="4" width="18.6640625" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -528,7 +521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -538,8 +531,23 @@
       <c r="C2">
         <v>122</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="D2">
+        <f xml:space="preserve"> B2-C2</f>
+        <v>470</v>
+      </c>
+      <c r="E2">
+        <v>247.072</v>
+      </c>
+      <c r="F2">
+        <f>D2-E2</f>
+        <v>222.928</v>
+      </c>
+      <c r="G2">
+        <f xml:space="preserve"> E2/D2</f>
+        <v>0.52568510638297872</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -549,8 +557,23 @@
       <c r="C3">
         <v>122</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="D3">
+        <f t="shared" ref="D3:E16" si="0" xml:space="preserve"> B3-C3</f>
+        <v>404</v>
+      </c>
+      <c r="E3">
+        <v>219.71199999999999</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F15" si="1">D3-E3</f>
+        <v>184.28800000000001</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G16" si="2" xml:space="preserve"> E3/D3</f>
+        <v>0.54384158415841577</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -560,8 +583,23 @@
       <c r="C4">
         <v>120</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>432</v>
+      </c>
+      <c r="E4">
+        <v>231.61199999999999</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>200.38800000000001</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="2"/>
+        <v>0.53613888888888883</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -571,8 +609,23 @@
       <c r="C5">
         <v>116</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>428</v>
+      </c>
+      <c r="E5">
+        <v>229.77199999999999</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>198.22800000000001</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="2"/>
+        <v>0.53685046728971964</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -582,8 +635,23 @@
       <c r="C6">
         <v>120</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>488</v>
+      </c>
+      <c r="E6">
+        <v>253.292</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>234.708</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="2"/>
+        <v>0.51904098360655737</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -593,8 +661,23 @@
       <c r="C7">
         <v>126</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>422</v>
+      </c>
+      <c r="E7">
+        <v>218.892</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>203.108</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="2"/>
+        <v>0.5187014218009478</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -604,8 +687,23 @@
       <c r="C8">
         <v>166</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>406</v>
+      </c>
+      <c r="E8">
+        <v>202.352</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>203.648</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="2"/>
+        <v>0.49840394088669954</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -615,8 +713,23 @@
       <c r="C9">
         <v>216</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>364</v>
+      </c>
+      <c r="E9">
+        <v>204.392</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>159.608</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="2"/>
+        <v>0.56151648351648353</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -626,8 +739,23 @@
       <c r="C10">
         <v>164</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>356</v>
+      </c>
+      <c r="E10">
+        <v>197.512</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>158.488</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="2"/>
+        <v>0.55480898876404494</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -637,8 +765,23 @@
       <c r="C11">
         <v>82</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>502</v>
+      </c>
+      <c r="E11">
+        <v>247.69200000000001</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="1"/>
+        <v>254.30799999999999</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="2"/>
+        <v>0.49341035856573706</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -648,8 +791,23 @@
       <c r="C12">
         <v>82</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>410</v>
+      </c>
+      <c r="E12">
+        <v>208.792</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="1"/>
+        <v>201.208</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="2"/>
+        <v>0.50924878048780486</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -659,8 +817,23 @@
       <c r="C13">
         <v>122</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>414</v>
+      </c>
+      <c r="E13">
+        <v>210.15199999999999</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>203.84800000000001</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="2"/>
+        <v>0.50761352657004832</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -670,8 +843,23 @@
       <c r="C14">
         <v>164</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>468</v>
+      </c>
+      <c r="E14">
+        <v>237.13200000000001</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="1"/>
+        <v>230.86799999999999</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="2"/>
+        <v>0.50669230769230766</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -681,8 +869,23 @@
       <c r="C15">
         <v>78</v>
       </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>402</v>
+      </c>
+      <c r="E15">
+        <v>206.41200000000001</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>195.58799999999999</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="2"/>
+        <v>0.51346268656716421</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -692,37 +895,343 @@
       <c r="C16">
         <v>120</v>
       </c>
-    </row>
-    <row r="18" spans="4:8">
-      <c r="D18" t="s">
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>420</v>
+      </c>
+      <c r="E16">
+        <v>212.31200000000001</v>
+      </c>
+      <c r="F16">
+        <f>D16-E16</f>
+        <v>207.68799999999999</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="2"/>
+        <v>0.5055047619047619</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F24A9CE3-FD7E-554E-BA11-1ABF52C511E2}">
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="19" spans="4:8">
-      <c r="D19" t="s">
+      <c r="C1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" spans="4:8">
-      <c r="D20" t="s">
+      <c r="E1" t="s">
         <v>26</v>
       </c>
-      <c r="E20" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>259.12</v>
+      </c>
+      <c r="B2">
+        <v>12.048</v>
+      </c>
+      <c r="C2">
+        <f xml:space="preserve"> A2-B2</f>
+        <v>247.072</v>
+      </c>
+      <c r="D2">
+        <v>247.072</v>
+      </c>
+      <c r="E2">
+        <f>D2-C2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>231.76</v>
+      </c>
+      <c r="B3">
+        <v>12.048</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C16" si="0" xml:space="preserve"> A3-B3</f>
+        <v>219.71199999999999</v>
+      </c>
+      <c r="D3">
+        <v>219.71199999999999</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E16" si="1">D3-C3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>243.66</v>
+      </c>
+      <c r="B4">
+        <v>12.048</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>231.61199999999999</v>
+      </c>
+      <c r="D4">
+        <v>231.61199999999999</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>241.82</v>
+      </c>
+      <c r="B5">
+        <v>12.048</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>229.77199999999999</v>
+      </c>
+      <c r="D5">
+        <v>229.77199999999999</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>265.33999999999997</v>
+      </c>
+      <c r="B6">
+        <v>12.048</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>253.29199999999997</v>
+      </c>
+      <c r="D6">
+        <v>253.292</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>230.94</v>
+      </c>
+      <c r="B7">
+        <v>12.048</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>218.892</v>
+      </c>
+      <c r="D7">
+        <v>218.892</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>214.4</v>
+      </c>
+      <c r="B8">
+        <v>12.048</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>202.352</v>
+      </c>
+      <c r="D8">
+        <v>202.352</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>216.44</v>
+      </c>
+      <c r="B9">
+        <v>12.048</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>204.392</v>
+      </c>
+      <c r="D9">
+        <v>204.392</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>209.56</v>
+      </c>
+      <c r="B10">
+        <v>12.048</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>197.512</v>
+      </c>
+      <c r="D10">
+        <v>197.512</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>259.74</v>
+      </c>
+      <c r="B11">
+        <v>12.048</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>247.69200000000001</v>
+      </c>
+      <c r="D11">
+        <v>247.69200000000001</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>220.84</v>
+      </c>
+      <c r="B12">
+        <v>12.048</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>208.792</v>
+      </c>
+      <c r="D12">
+        <v>208.792</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>222.2</v>
+      </c>
+      <c r="B13">
+        <v>12.048</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>210.15199999999999</v>
+      </c>
+      <c r="D13">
+        <v>210.15199999999999</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>249.18</v>
+      </c>
+      <c r="B14">
+        <v>12.048</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>237.13200000000001</v>
+      </c>
+      <c r="D14">
+        <v>237.13200000000001</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>218.46</v>
+      </c>
+      <c r="B15">
+        <v>12.048</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>206.41200000000001</v>
+      </c>
+      <c r="D15">
+        <v>206.41200000000001</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>224.36</v>
+      </c>
+      <c r="B16">
+        <v>12.048</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>212.31200000000001</v>
+      </c>
+      <c r="D16">
+        <v>212.31200000000001</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>22</v>
       </c>
-      <c r="G20" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="4:8">
-      <c r="D21" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" t="s">
-        <v>29</v>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>12.048</v>
       </c>
     </row>
   </sheetData>

--- a/Yield/RES_field_datasheet_jdx.xlsx
+++ b/Yield/RES_field_datasheet_jdx.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhangdakui/Documents/GitHub/ERW/Yield/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B51E251-522D-E044-A9F1-CF4D4680251C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393CA23E-1C92-4545-9116-C192AA0FEDEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2820" yWindow="4340" windowWidth="27420" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="draft" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -558,7 +558,7 @@
         <v>122</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:E16" si="0" xml:space="preserve"> B3-C3</f>
+        <f t="shared" ref="D3:D16" si="0" xml:space="preserve"> B3-C3</f>
         <v>404</v>
       </c>
       <c r="E3">

--- a/Yield/RES_field_datasheet_jdx.xlsx
+++ b/Yield/RES_field_datasheet_jdx.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhangdakui/Documents/GitHub/ERW/Yield/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhang\Documents\GitHub\ERW\Yield\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393CA23E-1C92-4545-9116-C192AA0FEDEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2820" yWindow="4340" windowWidth="27420" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2820" yWindow="4335" windowWidth="27420" windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="draft" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -123,8 +122,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -488,17 +487,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="26.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
     <col min="4" max="4" width="18.6640625" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -521,7 +520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -547,7 +546,7 @@
         <v>0.52568510638297872</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -573,7 +572,7 @@
         <v>0.54384158415841577</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -599,7 +598,7 @@
         <v>0.53613888888888883</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -625,7 +624,7 @@
         <v>0.53685046728971964</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -651,7 +650,7 @@
         <v>0.51904098360655737</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -677,7 +676,7 @@
         <v>0.5187014218009478</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -703,7 +702,7 @@
         <v>0.49840394088669954</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -729,7 +728,7 @@
         <v>0.56151648351648353</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -755,7 +754,7 @@
         <v>0.55480898876404494</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -781,7 +780,7 @@
         <v>0.49341035856573706</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -807,7 +806,7 @@
         <v>0.50924878048780486</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -833,7 +832,7 @@
         <v>0.50761352657004832</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -859,7 +858,7 @@
         <v>0.50669230769230766</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -885,7 +884,7 @@
         <v>0.51346268656716421</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -917,15 +916,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F24A9CE3-FD7E-554E-BA11-1ABF52C511E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.83203125" customWidth="1"/>
+    <col min="1" max="1" width="21.77734375" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -939,7 +938,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>259.12</v>
       </c>
@@ -958,7 +957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>231.76</v>
       </c>
@@ -977,7 +976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>243.66</v>
       </c>
@@ -996,7 +995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>241.82</v>
       </c>
@@ -1015,7 +1014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>265.33999999999997</v>
       </c>
@@ -1034,7 +1033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>230.94</v>
       </c>
@@ -1053,7 +1052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>214.4</v>
       </c>
@@ -1072,7 +1071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>216.44</v>
       </c>
@@ -1091,7 +1090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>209.56</v>
       </c>
@@ -1110,7 +1109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>259.74</v>
       </c>
@@ -1129,7 +1128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>220.84</v>
       </c>
@@ -1148,7 +1147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>222.2</v>
       </c>
@@ -1167,7 +1166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>249.18</v>
       </c>
@@ -1186,7 +1185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>218.46</v>
       </c>
@@ -1205,7 +1204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>224.36</v>
       </c>
@@ -1224,12 +1223,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1">
       <c r="A19">
         <v>12.048</v>
       </c>
